--- a/Categoría/US_Categoría.xlsx
+++ b/Categoría/US_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.4629491399917833</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>113.9149343886617</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.5195503020859663</v>
+        <v>0.5273682090745134</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1009,7 +1009,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>3.209204996757074</v>
+        <v>3.209204996757075</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1972,13 +1972,13 @@
         <v>0.3410284524149643</v>
       </c>
       <c r="C69" s="2">
-        <v>114.8063759508347</v>
+        <v>114.8063759508346</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>0.3915224071788373</v>
+        <v>0.3915224071788372</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2012,7 +2012,7 @@
         <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>0.8464465441640308</v>
+        <v>0.8464465441640304</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2513,7 +2513,7 @@
         <v>105</v>
       </c>
       <c r="B101" s="2">
-        <v>2.295159510478515</v>
+        <v>2.295159510478514</v>
       </c>
       <c r="C101" s="2">
         <v>106.5526674445129</v>
@@ -2522,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="E101" s="2">
-        <v>2.445553680521282</v>
+        <v>2.445553680521281</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2904,7 +2904,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>5.162609750584102</v>
+        <v>5.162609750584101</v>
       </c>
       <c r="C124" s="2">
         <v>121.5486258559389</v>
@@ -2913,7 +2913,7 @@
         <v>6</v>
       </c>
       <c r="E124" s="2">
-        <v>6.275081210139689</v>
+        <v>6.275081210139688</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2924,7 +2924,7 @@
         <v>10.13281918479449</v>
       </c>
       <c r="C125" s="2">
-        <v>115.6998554597055</v>
+        <v>115.6998554597054</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>6</v>
